--- a/Output/VO2maxQC/quality_differences.MLAmethod.xlsx
+++ b/Output/VO2maxQC/quality_differences.MLAmethod.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -432,10 +432,10 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>6.666666666666667</v>
+        <v>5.88235294117647</v>
       </c>
     </row>
     <row r="5">
@@ -451,10 +451,10 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>73.33333333333333</v>
+        <v>64.70588235294117</v>
       </c>
     </row>
     <row r="6">
@@ -464,13 +464,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>29.41176470588236</v>
       </c>
     </row>
     <row r="7">
@@ -486,29 +486,26 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Iben</t>
-        </is>
-      </c>
-      <c r="B8" t="b">
-        <v>0</v>
+          <t>Clara og Iben</t>
+        </is>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="D8">
-        <v>11</v>
-      </c>
       <c r="E8">
-        <v>18.18181818181818</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -518,16 +515,16 @@
         </is>
       </c>
       <c r="B9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E9">
-        <v>72.72727272727273</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="10">
@@ -536,33 +533,33 @@
           <t>Iben</t>
         </is>
       </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
       <c r="C10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>9.090909090909092</v>
+        <v>61.53846153846154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Malte</t>
-        </is>
-      </c>
-      <c r="B11" t="b">
-        <v>0</v>
+          <t>Iben</t>
+        </is>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="E11">
-        <v>7.692307692307693</v>
+        <v>23.07692307692308</v>
       </c>
     </row>
     <row r="12">
@@ -572,16 +569,16 @@
         </is>
       </c>
       <c r="B12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>104</v>
       </c>
       <c r="E12">
-        <v>88.46153846153845</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="13">
@@ -590,39 +587,39 @@
           <t>Malte</t>
         </is>
       </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
       <c r="C13">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="D13">
         <v>104</v>
       </c>
       <c r="E13">
-        <v>3.846153846153846</v>
+        <v>88.46153846153845</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Malte og Iben</t>
-        </is>
-      </c>
-      <c r="B14" t="b">
-        <v>0</v>
+          <t>Malte</t>
+        </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>3.846153846153846</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marie Louise</t>
+          <t>Malte og Iben</t>
         </is>
       </c>
       <c r="B15" t="b">
@@ -632,10 +629,10 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>12.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -645,16 +642,16 @@
         </is>
       </c>
       <c r="B16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>8</v>
       </c>
       <c r="E16">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="17">
@@ -663,58 +660,77 @@
           <t>Marie Louise</t>
         </is>
       </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
       <c r="C17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
-        <v>12.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Marie Louise</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Simon</t>
         </is>
       </c>
-      <c r="B18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
+      <c r="B19" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
         <v>100</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="b">
-        <v>1</v>
-      </c>
-      <c r="C19">
+    <row r="20">
+      <c r="B20" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20">
         <v>4</v>
       </c>
-      <c r="D19">
-        <v>6</v>
-      </c>
-      <c r="E19">
-        <v>66.66666666666666</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20">
-        <v>2</v>
-      </c>
       <c r="D20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>33.33333333333333</v>
+        <v>57.14285714285714</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21">
+        <v>42.85714285714285</v>
       </c>
     </row>
   </sheetData>
